--- a/output/2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,6 @@
           <t>051 6920730</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Ragione sociale completa 'Aspirnova S.n.c. di Gentili Michele e Paravidino Luca'. Nessuna email trovata.</t>
@@ -586,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -616,7 +615,6 @@
           <t>+39 051 6647616</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Attiva da 40 anni, confermata su reteimprese, paginegialle, sito ufficiale.</t>
@@ -624,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -634,7 +632,6 @@
           <t>Tecno Aria Srl</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Parma</t>
@@ -662,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -687,8 +684,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Confermata su kompass, ufficiocamerale, sito ufficiale.</t>
@@ -696,7 +691,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -726,7 +721,6 @@
           <t>+39 0536 071051</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Attiva da oltre 35 anni, opera su MO/BO/RE/Mantova/ER.</t>
@@ -734,7 +728,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -764,7 +758,6 @@
           <t>051 6605422 / 338 2190683</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Confermata sede legale e P.IVA 03440051203 (REA 519235).</t>
@@ -772,7 +765,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -814,7 +807,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -856,7 +849,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -898,7 +891,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -928,7 +921,6 @@
           <t>0521 682004 / 0521 682008</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Confermata su kompass, idecoimpianti.it, petfoodtechnology.com.</t>
@@ -936,7 +928,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -978,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1000,6 @@
           <t>+39 0523 856231</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Confermata: due sedi, Carpaneto Piacentino (produzione) e Gropparello (ricambi).</t>
@@ -1016,7 +1007,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1037,6 @@
           <t>+39 0523 524066</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Confermata, parte del Gruppo Belloni, presenza internazionale (52 paesi).</t>
@@ -1054,7 +1044,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1158,6 @@
           <t>0547 335444 / 0543 795959</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Fondata 2003 (esperienza dal 1993), certificazione ISO 9001:2015.</t>
@@ -1176,7 +1165,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1195,6 @@
           <t>0543 725482</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Attiva da oltre 30 anni, gestione familiare Turchi.</t>
@@ -1214,7 +1202,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1244,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1274,6 @@
           <t>0541 957680</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Confermata su paginebianche, ventilsystem.net.</t>
@@ -1294,7 +1281,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1323,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1365,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1395,6 @@
           <t>+39 0532 52381 / +39 0532 692384</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Fondata nel 1979, certificazioni ISO 9001/14001.</t>
@@ -1416,7 +1402,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1441,8 +1427,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Fondata 1991, 20-49 dipendenti, ATECO 43.22.00; confermata su europages, reportaziende.</t>
@@ -1450,7 +1434,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1506,6 @@
           <t>+39 0383 872776</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Sede secondaria a Lugagnano Val d'Arda (PC) confermata; sede principale a Borgo Priolo (PV).</t>
@@ -1555,7 +1538,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>contactus@worky-italy.com</t>
@@ -1598,7 +1580,6 @@
           <t>0522667168</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Indirizzo esatto: Via della Costituzione 17-19, 42047 Rolo (RE). Azienda storica (50 anni).</t>
